--- a/data/testdata.xlsx
+++ b/data/testdata.xlsx
@@ -11,66 +11,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>ScenarioName</t>
   </si>
   <si>
-    <t>ElementName</t>
-  </si>
-  <si>
-    <t>TestData</t>
-  </si>
-  <si>
-    <t>DataType</t>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>reportTypeDropdown</t>
   </si>
   <si>
     <t>Successful login with valid credentials</t>
   </si>
   <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>testuser@example.com</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>Password123!</t>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Failed login with invalid credentials</t>
   </si>
   <si>
-    <t>invaliduser@example.com</t>
+    <t>invaliduser</t>
   </si>
   <si>
     <t>wrongpassword</t>
   </si>
   <si>
-    <t>Successful login</t>
-  </si>
-  <si>
-    <t>Navigate to dashboard and verify elements</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>User can logout successfully</t>
-  </si>
-  <si>
     <t>Verify table data with dropdown selection</t>
-  </si>
-  <si>
-    <t>reportTypeDropdown</t>
   </si>
   <si>
     <t>Monthly</t>
@@ -459,13 +435,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -498,13 +472,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -512,100 +486,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/testdata.xlsx
+++ b/data/testdata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>ScenarioName</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>Monthly</t>
+  </si>
+  <si>
+    <t>End-to-end purchase flow</t>
+  </si>
+  <si>
+    <t>Access dashboard after successful login</t>
   </si>
 </sst>
 </file>
@@ -435,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -498,8 +504,30 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/testdata.xlsx
+++ b/data/testdata.xlsx
@@ -1,77 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_33EE948F46AEBF936379811CFC2509035EF8FFB8" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{AE7145F8-EC66-4F0F-8F66-8CA4D3D51F20}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="TestData" state="visible" r:id="rId4"/>
+    <sheet name="TestData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ScenarioName</t>
   </si>
   <si>
-    <t>username</t>
-  </si>
-  <si>
     <t>password</t>
   </si>
   <si>
     <t>reportTypeDropdown</t>
   </si>
   <si>
-    <t>Successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>standard_user</t>
-  </si>
-  <si>
     <t>secret_sauce</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Failed login with invalid credentials</t>
-  </si>
-  <si>
-    <t>invaliduser</t>
-  </si>
-  <si>
-    <t>wrongpassword</t>
-  </si>
-  <si>
-    <t>Verify table data with dropdown selection</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>End-to-end purchase flow</t>
-  </si>
-  <si>
-    <t>Access dashboard after successful login</t>
+    <t>email</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ashok@gmail.com</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TESTSCENARIO</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -96,15 +101,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -440,94 +448,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{1D7DA36E-FA21-47E5-92C5-D20A8ED35A00}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
 </worksheet>
 </file>